--- a/results/job_matches_2026-10-14.xlsx
+++ b/results/job_matches_2026-10-14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,52 +526,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
+          <t>Full Stack Developer - Node/ React/ AWS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8800b92970b28dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=9f52c644d636f81c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise Architecture</t>
+          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sunrise, FL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,7 +579,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,49 +589,49 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41e5aaffae63b67</t>
+          <t>https://www.indeed.com/viewjob?jk=8800b92970b28dfb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Store AI Agent - Onshore Data Engineer (Python, Pytorch, NodeJS)</t>
+          <t>Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Sunrise, FL, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d863cb3c38f06b</t>
+          <t>https://www.indeed.com/viewjob?jk=f41e5aaffae63b67</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SS - Onshore Data Engineer (Python, Pytorch)</t>
+          <t>Store AI Agent - Onshore Data Engineer (Python, Pytorch, NodeJS)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1804ca13c879a613</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d863cb3c38f06b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SS - Onshore Data Engineer (Python, Pytorch)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a90d59b7cf9d6b41</t>
+          <t>https://www.indeed.com/viewjob?jk=1804ca13c879a613</t>
         </is>
       </c>
     </row>
@@ -736,17 +736,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, Data Management - East</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NJ, USA USA</t>
+          <t>North Little Rock, AR, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,42 +754,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31d93ef09b2d5ada</t>
+          <t>https://www.indeed.com/viewjob?jk=a90d59b7cf9d6b41</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Systems Engineer, Data Management - East</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>NJ, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3693c9cd5da878e</t>
+          <t>https://www.indeed.com/viewjob?jk=31d93ef09b2d5ada</t>
         </is>
       </c>
     </row>
@@ -841,25 +841,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Specialist, Yield Management - GTM Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>Dearborn, MI, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,24 +869,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87fe4de2e714f22</t>
+          <t>https://www.indeed.com/viewjob?jk=0f50e110d31ed36a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Specialist, Yield Management - GTM Data Engineer</t>
+          <t>Full-Stack Senior Developers</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Natoli Engineering</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dearborn, MI, USA USA</t>
+          <t>Saint Charles, MO, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f50e110d31ed36a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e928d074bdf699</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Developers</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Natoli Engineering</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saint Charles, MO, USA USA</t>
+          <t>Adelphi, MD, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,19 +939,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e928d074bdf699</t>
+          <t>https://www.indeed.com/viewjob?jk=705ae459e19365e9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Modeler Engineer Senior I</t>
+          <t>Analytics Platform Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a79945a69d44134</t>
+          <t>https://www.indeed.com/viewjob?jk=e213d5c6c5856442</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer - Senior Associate</t>
+          <t>Business Intelligence Data Modeler Engineer Senior I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1034,34 +1034,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Azure</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e213d5c6c5856442</t>
+          <t>https://www.indeed.com/viewjob?jk=3a79945a69d44134</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer Senior Consultant I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Adelphi, MD, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,32 +1079,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705ae459e19365e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e045cc6a43c6b4be</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer Senior Consultant I</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,24 +1114,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e045cc6a43c6b4be</t>
+          <t>https://www.indeed.com/viewjob?jk=d106c1338953198c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>DevOps / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>Alchemy Cloud</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, GCP, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d106c1338953198c</t>
+          <t>https://www.indeed.com/viewjob?jk=5fb1e7413def7791</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps / Infrastructure Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alchemy Cloud</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Adelphi, MD, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, GCP, MySQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb1e7413def7791</t>
+          <t>https://www.indeed.com/viewjob?jk=c1eb27537b9273b0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Health Data Modeler</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Adelphi, MD, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,24 +1219,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1eb27537b9273b0</t>
+          <t>https://www.indeed.com/viewjob?jk=339b2689dab59d45</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Health Data Modeler</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>McGuireWoods LLP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,24 +1254,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=339b2689dab59d45</t>
+          <t>https://www.indeed.com/viewjob?jk=166247ae6ba80226</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Full Stack Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>McGuireWoods LLP</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Conshohocken, PA, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=166247ae6ba80226</t>
+          <t>https://www.indeed.com/viewjob?jk=5c476b35c41be97e</t>
         </is>
       </c>
     </row>
@@ -1331,35 +1331,35 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Engineer II</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Mutual of Omaha Mortgage</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Snowflake, SQL Server, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c476b35c41be97e</t>
+          <t>https://www.indeed.com/viewjob?jk=d76024005e194d69</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>US- Java Engineer - Pricing</t>
+          <t>UKG Integration Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MoneyGram</t>
+          <t>Vnsure Business Solution</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, HBase, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,24 +1429,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9eb4c3615ab029</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd00894ae3ccf24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UKG Integration Developer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vnsure Business Solution</t>
+          <t>IHG Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, Data Modeling, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,24 +1464,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd00894ae3ccf24</t>
+          <t>https://www.indeed.com/viewjob?jk=a595a72e3d3f9968</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Sr. Support &amp; Post-Release Quality Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IHG Hotels &amp; Resorts</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Berkeley Heights, NJ, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, Data Modeling, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,32 +1499,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a595a72e3d3f9968</t>
+          <t>https://www.indeed.com/viewjob?jk=5898f422bfe5208e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Support &amp; Post-Release Quality Engineer</t>
+          <t>Engineer Data II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>IGT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, USA USA</t>
+          <t>Las Vegas, NV, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,24 +1534,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5898f422bfe5208e</t>
+          <t>https://www.indeed.com/viewjob?jk=0da8f75cf9c2b540</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Engineer Data II</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IGT</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,24 +1569,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da8f75cf9c2b540</t>
+          <t>https://www.indeed.com/viewjob?jk=9d247a00ef97cfce</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Software Engineer II - Full Stack &amp; AI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>O'Fallon, MO, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,34 +1594,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d247a00ef97cfce</t>
+          <t>https://www.indeed.com/viewjob?jk=eadfe87c770bfddc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack &amp; AI</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Maven</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,24 +1639,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadfe87c770bfddc</t>
+          <t>https://www.indeed.com/viewjob?jk=25ed6474978b921d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Louisville, KY, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,34 +1664,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6352c20c3850230b</t>
+          <t>https://www.indeed.com/viewjob?jk=b2de87a09b47cb83</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IT Analyst III - Database Administrator</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>State of Utah</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Taylorsville, UT, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,24 +1709,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2de87a09b47cb83</t>
+          <t>https://www.indeed.com/viewjob?jk=f0318ab669e83c7d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IT Analyst III - Database Administrator</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>State of Utah</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Taylorsville, UT, USA USA</t>
+          <t>Louisville, KY, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,34 +1734,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0318ab669e83c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=6352c20c3850230b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PostgreSQL and MongoDB</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FL, USA USA</t>
+          <t>Kennesaw, GA, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,24 +1779,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0c3e70a1257e99</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Jr. Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,24 +1814,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=5c700c5ee304c350</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jr. Cloud Automation Engineer</t>
+          <t>.Net Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,24 +1849,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c700c5ee304c350</t>
+          <t>https://www.indeed.com/viewjob?jk=dded0af6d2070543</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>.Net Engineer</t>
+          <t>Applications Administrator IV (IT Systems)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>University of Louisville</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, USA USA</t>
+          <t>Louisville, KY, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dded0af6d2070543</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1dc43bf4f44c94</t>
         </is>
       </c>
     </row>
@@ -1926,17 +1926,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Applications Administrator IV (IT Systems)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>University of Louisville</t>
+          <t>o3 Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Louisville, KY, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,59 +1954,59 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1dc43bf4f44c94</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea8f0126c1468fe</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>o3 Solutions</t>
+          <t>SJSU Research Foundation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>San Jose, CA, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, Scala, Snowflake, Oracle, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea8f0126c1468fe</t>
+          <t>https://www.indeed.com/viewjob?jk=e1de3366eafd1cc6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Solero Workforce Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>FL, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,34 +2014,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Dimensional Modeling, Dimension Tables, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5cdfdff452dafc</t>
+          <t>https://www.indeed.com/viewjob?jk=2830c33b549b2199</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Marketing Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SJSU Research Foundation</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Jose, CA, USA USA</t>
+          <t>La Mirada, CA, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,34 +2049,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, Scala, Snowflake, Oracle, ETL, ELT, Tableau</t>
+          <t>AWS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1de3366eafd1cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=91f01e86c7eb2733</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Databrick Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shift4</t>
+          <t>SDG Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Center Valley, PA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Kafka, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,24 +2094,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41844b46aff0cb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3e85cb5ceb58b2cf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Marketing Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>La Mirada, CA, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,34 +2119,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Dimensional Modeling, Dimension Tables, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f01e86c7eb2733</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5cdfdff452dafc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Python- AI Software Engineer III</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Shift4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wilmington, DE, USA USA</t>
+          <t>Center Valley, PA, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, ECS, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Kafka, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,24 +2164,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5aa4a9fbcd4b6c3</t>
+          <t>https://www.indeed.com/viewjob?jk=41844b46aff0cb0b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Databrick Data Engineering Consultant</t>
+          <t>Senior Software Engineer - Java Full Stack &amp; AI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SDG Group</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>O'Fallon, MO, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,34 +2189,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e85cb5ceb58b2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=7e59f1d190af6811</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Solero Workforce Solutions</t>
+          <t>HARVEST GROUP</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FL, USA USA</t>
+          <t>Cincinnati, OH, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2224,34 +2224,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2830c33b549b2199</t>
+          <t>https://www.indeed.com/viewjob?jk=072ead67167c5fa8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java Full Stack &amp; AI</t>
+          <t>Senior Software Applications Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2259,34 +2259,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, ELT, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbc5b57747195bb1</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2b4867303bf280</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer I / II — AWS &amp; .NET</t>
+          <t>Security Engineer (Application Security)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Young Living Essential Oils</t>
+          <t>Blue Cross Blue Shield</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lehi, UT, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,32 +2304,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=527fb8088c169f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=c00d7a111fdf4824</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HARVEST GROUP</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, USA USA</t>
+          <t>Lebanon, NJ, USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,67 +2339,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072ead67167c5fa8</t>
+          <t>https://www.indeed.com/viewjob?jk=d3f6955e62075655</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Applications Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Mountain View, CA, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Azure, Databricks, GCP, Spark, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2b4867303bf280</t>
+          <t>https://www.indeed.com/viewjob?jk=fc0f0441157327ec</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Security Engineer (Application Security)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,24 +2409,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00d7a111fdf4824</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb2022242ed43e7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>DevOps Engineer, Platform</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,34 +2434,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3f6955e62075655</t>
+          <t>https://www.indeed.com/viewjob?jk=9968e46f0d946d92</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - DevOps (Plex)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Mayfield Heights, OH, USA USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Terraform</t>
+          <t>AWS, Azure, Kafka, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2479,24 +2479,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb2022242ed43e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8cadc6544ff917</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2514,24 +2514,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9968e46f0d946d92</t>
+          <t>https://www.indeed.com/viewjob?jk=e4483784feda6d19</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - DevOps (Plex)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>Friant &amp; Associates</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mayfield Heights, OH, USA USA</t>
+          <t>San Leandro, CA, USA USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2539,77 +2539,77 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad8cadc6544ff917</t>
+          <t>https://www.indeed.com/viewjob?jk=d4182938ad6c7715</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Infrastructure &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>OptionMetrics</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4483784feda6d19</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d92cc7208b2a4a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Friant &amp; Associates</t>
+          <t>Storm3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Leandro, CA, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,24 +2619,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4182938ad6c7715</t>
+          <t>https://www.indeed.com/viewjob?jk=f06e499ccf997308</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Development Systems Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,24 +2654,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a034f20a9a1e8675</t>
+          <t>https://www.indeed.com/viewjob?jk=671aed3088e72832</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shield Healthcare</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Valencia, CA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb7ae63ee72e66e</t>
+          <t>https://www.indeed.com/viewjob?jk=a034f20a9a1e8675</t>
         </is>
       </c>
     </row>
@@ -2731,17 +2731,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; DevOps Engineer</t>
+          <t>Service Delivery Center, Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OptionMetrics</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Raleigh, NC, USA USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2749,34 +2749,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d92cc7208b2a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=b8889c03578c4693</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Development Engineer III - Java Stack</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Storm3</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,34 +2784,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06e499ccf997308</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a67dcea3b9163a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Development Systems Engineer</t>
+          <t>Engineer, Customer Support and Analytics</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Warren, MI, USA USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,34 +2819,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671aed3088e72832</t>
+          <t>https://www.indeed.com/viewjob?jk=4c2a4c12238268f0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Senior DevOps Engineer</t>
+          <t>Senior Full Stack .NET Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2854,34 +2854,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
+          <t>RDS, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8889c03578c4693</t>
+          <t>https://www.indeed.com/viewjob?jk=324384e3bfc85ae8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Development Engineer III - Java Stack</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2899,24 +2899,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a67dcea3b9163a</t>
+          <t>https://www.indeed.com/viewjob?jk=957d4afb6a9b1121</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer, Customer Support and Analytics</t>
+          <t>Sr. Infrastructure Solutions Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Warren, MI, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2924,42 +2924,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, ETL, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c2a4c12238268f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d224d690c8e329fc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer IS - Remote</t>
+          <t>Infrastructure Solutions Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Plainview, TX, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, NoSQL, DataOps, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2969,24 +2969,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0361db4f39d8edb9</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7f4e300e647e15</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Vehicle Quality Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>OneKey MLS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Warren, MI, USA USA</t>
+          <t>Farmingdale, NY, USA USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3004,24 +3004,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744a3cb2d6fb585e</t>
+          <t>https://www.indeed.com/viewjob?jk=75651bec84129cee</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer (Two Positions), P3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>United Nations</t>
+          <t>AnewHealth</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Cleveland, OH, USA USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ETL, ELT, dbt, Azure DevOps, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3039,24 +3039,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94213dc00fbf6a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=9b077b090cd4d1ef</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III, Data Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3074,24 +3074,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60fb6c37a0a7b7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=dbdb7a9bff45af0a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Platform Engineer / AI-MLOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AnewHealth</t>
+          <t>EAPPS TECH LLC dba Magicforce</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cleveland, OH, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3109,24 +3109,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b077b090cd4d1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf9bfd089ca9e4c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>OneKey MLS</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Farmingdale, NY, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3144,24 +3144,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75651bec84129cee</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ba22ee549c1229</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Platform Operations - Remote</t>
+          <t>Senior Data Engineer IS - Remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, USA USA</t>
+          <t>Plainview, TX, USA USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, DynamoDB, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, NoSQL, DataOps, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3179,24 +3179,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbdb7a9bff45af0a</t>
+          <t>https://www.indeed.com/viewjob?jk=0361db4f39d8edb9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer / AI-MLOps Engineer</t>
+          <t>Senior Data Engineer - Vehicle Quality Engineering</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EAPPS TECH LLC dba Magicforce</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Warren, MI, USA USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf9bfd089ca9e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=744a3cb2d6fb585e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer 2 – Java, Generative AI, RAG &amp; Cloud Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Hopkins, MN, USA USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3249,24 +3249,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ba22ee549c1229</t>
+          <t>https://www.indeed.com/viewjob?jk=fdfcf5a045e444da</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer IS - Remote</t>
+          <t>I&amp;T Data Services Analyst</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>City of Charlotte, NC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lubbock, TX, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, NoSQL, DataOps, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3284,24 +3284,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd883687922931bc</t>
+          <t>https://www.indeed.com/viewjob?jk=db0e9d7d87a6771b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer - (React, GCP, Node, Angular)</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Strategic Operational Solutions</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Richmond, VA, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3319,24 +3319,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31743146b6a0d95d</t>
+          <t>https://www.indeed.com/viewjob?jk=1293dae16bacfe7e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Java, Generative AI, RAG &amp; Cloud Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hopkins, MN, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3344,34 +3344,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdfcf5a045e444da</t>
+          <t>https://www.indeed.com/viewjob?jk=02e9aac59a0c85c9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer, S3 storage</t>
+          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fremont, CA, USA USA</t>
+          <t>Malvern, PA, USA USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Spark, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3389,24 +3389,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcdf69eb1ba1e50c</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef875202e4d9683</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Site Reliability Engineer SRE - Internationalisation</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Strategic Operational Solutions</t>
+          <t>FUKU</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3414,157 +3414,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, MySQL, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1293dae16bacfe7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Siemens Healthineers</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Malvern, PA, USA USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef875202e4d9683</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>I&amp;T Data Services Analyst</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>City of Charlotte, NC</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, USA USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db0e9d7d87a6771b</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Web Site Developer Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Arizona State University</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, USA USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, CI/CD, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86b7bf97bf3d08af</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Sr Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Equiniti</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Woburn, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4b84101d3572ca</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4d0d149bc3cb1a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-14.xlsx
+++ b/results/job_matches_2026-10-14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Systems Architect - TS/SCI w/ Poly required</t>
+          <t>Systems Architect, SME</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Warrenton, VA, USA USA</t>
+          <t>Tysons Corner, VA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -479,37 +479,37 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b2560066a45e46</t>
+          <t>https://www.indeed.com/viewjob?jk=74acab416de0ee2f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IT Consultant - Cloud Specialist L2</t>
+          <t>Systems Architect - TS/SCI w/ Poly required</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hanover, NJ, USA USA</t>
+          <t>Warrenton, VA, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>23.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, IAM</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,14 +519,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c5b1d05ad98c56</t>
+          <t>https://www.indeed.com/viewjob?jk=51b2560066a45e46</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Node/ React/ AWS</t>
+          <t>IT Consultant - Cloud Specialist L2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -536,77 +536,77 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Hanover, NJ, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, IAM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f52c644d636f81c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c5b1d05ad98c56</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
+          <t>Full Stack Developer - Node/ React/ AWS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8800b92970b28dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=9f52c644d636f81c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise Architecture</t>
+          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunrise, FL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,49 +624,49 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41e5aaffae63b67</t>
+          <t>https://www.indeed.com/viewjob?jk=8800b92970b28dfb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Store AI Agent - Onshore Data Engineer (Python, Pytorch, NodeJS)</t>
+          <t>Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Sunrise, FL, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d863cb3c38f06b</t>
+          <t>https://www.indeed.com/viewjob?jk=f41e5aaffae63b67</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SS - Onshore Data Engineer (Python, Pytorch)</t>
+          <t>Store AI Agent - Onshore Data Engineer (Python, Pytorch, NodeJS)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -694,42 +694,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1804ca13c879a613</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d863cb3c38f06b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>SS - Onshore Data Engineer (Python, Pytorch)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Foundation Software, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Strongsville, OH, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e8721900a835a2</t>
+          <t>https://www.indeed.com/viewjob?jk=1804ca13c879a613</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, Data Management - East</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Foundation Software, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NJ, USA USA</t>
+          <t>Strongsville, OH, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31d93ef09b2d5ada</t>
+          <t>https://www.indeed.com/viewjob?jk=69e8721900a835a2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IT DevOps Engineer (Bilingual Chinese and English)</t>
+          <t>Senior Systems Engineer, Data Management - East</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SpeedX</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Montebello, CA, USA USA</t>
+          <t>NJ, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d923f0e84b3c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=31d93ef09b2d5ada</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Specialist, Yield Management - GTM Data Engineer</t>
+          <t>IT DevOps Engineer (Bilingual Chinese and English)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>SpeedX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dearborn, MI, USA USA</t>
+          <t>Montebello, CA, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,24 +869,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f50e110d31ed36a</t>
+          <t>https://www.indeed.com/viewjob?jk=91d923f0e84b3c2c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Developers</t>
+          <t>Sr. Specialist, Yield Management - GTM Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Natoli Engineering</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saint Charles, MO, USA USA</t>
+          <t>Dearborn, MI, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e928d074bdf699</t>
+          <t>https://www.indeed.com/viewjob?jk=0f50e110d31ed36a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Full-Stack Senior Developers</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>Natoli Engineering</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Adelphi, MD, USA USA</t>
+          <t>Saint Charles, MO, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,19 +939,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705ae459e19365e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e928d074bdf699</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer - Senior Associate</t>
+          <t>Business Intelligence Data Modeler Engineer Senior I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Azure</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e213d5c6c5856442</t>
+          <t>https://www.indeed.com/viewjob?jk=3a79945a69d44134</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Modeler Engineer Senior I</t>
+          <t>Analytics Platform Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1034,34 +1034,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a79945a69d44134</t>
+          <t>https://www.indeed.com/viewjob?jk=e213d5c6c5856442</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer Senior Consultant I</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Adelphi, MD, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,32 +1079,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e045cc6a43c6b4be</t>
+          <t>https://www.indeed.com/viewjob?jk=705ae459e19365e9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Software Engineer Senior Consultant I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,24 +1114,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d106c1338953198c</t>
+          <t>https://www.indeed.com/viewjob?jk=e045cc6a43c6b4be</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps / Infrastructure Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alchemy Cloud</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, GCP, MySQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb1e7413def7791</t>
+          <t>https://www.indeed.com/viewjob?jk=d106c1338953198c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>DevOps / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>Alchemy Cloud</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Adelphi, MD, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, GCP, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1eb27537b9273b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5fb1e7413def7791</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Health Data Modeler</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Adelphi, MD, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,24 +1219,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=339b2689dab59d45</t>
+          <t>https://www.indeed.com/viewjob?jk=c1eb27537b9273b0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Health Data Modeler</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>McGuireWoods LLP</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,24 +1254,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=166247ae6ba80226</t>
+          <t>https://www.indeed.com/viewjob?jk=339b2689dab59d45</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Engineer II</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c476b35c41be97e</t>
+          <t>https://www.indeed.com/viewjob?jk=faf7d5b09dec217c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Full Stack Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Conshohocken, PA, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, ELT</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf7d5b09dec217c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c476b35c41be97e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mutual of Omaha Mortgage</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,34 +1349,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Snowflake, SQL Server, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d76024005e194d69</t>
+          <t>https://www.indeed.com/viewjob?jk=954d7871d42f0836</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Mutual of Omaha Mortgage</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,34 +1384,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Snowflake, SQL Server, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=954d7871d42f0836</t>
+          <t>https://www.indeed.com/viewjob?jk=d76024005e194d69</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>UKG Integration Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vnsure Business Solution</t>
+          <t>Pennant Solutions Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Richmond, VA, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,34 +1419,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd00894ae3ccf24</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c84e90f22435c1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>UKG Integration Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IHG Hotels &amp; Resorts</t>
+          <t>Vnsure Business Solution</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, Data Modeling, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,24 +1464,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a595a72e3d3f9968</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd00894ae3ccf24</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Support &amp; Post-Release Quality Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>IHG Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, Data Modeling, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5898f422bfe5208e</t>
+          <t>https://www.indeed.com/viewjob?jk=a595a72e3d3f9968</t>
         </is>
       </c>
     </row>
@@ -1541,17 +1541,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Data Engineer - Materials Discovery Research Institute</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>UL Research Institutes</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Skokie, IL, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,34 +1559,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d247a00ef97cfce</t>
+          <t>https://www.indeed.com/viewjob?jk=f01d33f572b2baf0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack &amp; AI</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,34 +1594,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadfe87c770bfddc</t>
+          <t>https://www.indeed.com/viewjob?jk=9d247a00ef97cfce</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Software Engineer II - Full Stack &amp; AI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>O'Fallon, MO, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,24 +1639,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ed6474978b921d</t>
+          <t>https://www.indeed.com/viewjob?jk=eadfe87c770bfddc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Louisville, KY, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,34 +1664,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2de87a09b47cb83</t>
+          <t>https://www.indeed.com/viewjob?jk=6352c20c3850230b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IT Analyst III - Database Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>State of Utah</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Taylorsville, UT, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,24 +1709,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0318ab669e83c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2de87a09b47cb83</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>IT Analyst III - Database Administrator</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>State of Utah</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Louisville, KY, USA USA</t>
+          <t>Taylorsville, UT, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,17 +1734,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6352c20c3850230b</t>
+          <t>https://www.indeed.com/viewjob?jk=f0318ab669e83c7d</t>
         </is>
       </c>
     </row>
@@ -1856,17 +1856,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Applications Administrator IV (IT Systems)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>University of Louisville</t>
+          <t>AllianceBernstein</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Louisville, KY, USA USA</t>
+          <t>Nashville, TN, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Vertex AI, Scala, Snowflake, Data Modeling, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,24 +1884,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1dc43bf4f44c94</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae65d4effd1829d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AllianceBernstein</t>
+          <t>o3 Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Vertex AI, Scala, Snowflake, Data Modeling, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,42 +1919,42 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae65d4effd1829d</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea8f0126c1468fe</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>o3 Solutions</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Dimensional Modeling, Dimension Tables, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea8f0126c1468fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5cdfdff452dafc</t>
         </is>
       </c>
     </row>
@@ -1996,17 +1996,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Solero Workforce Solutions</t>
+          <t>Shift4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FL, USA USA</t>
+          <t>Center Valley, PA, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Kafka, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2830c33b549b2199</t>
+          <t>https://www.indeed.com/viewjob?jk=41844b46aff0cb0b</t>
         </is>
       </c>
     </row>
@@ -2101,17 +2101,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Solero Workforce Solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>FL, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,34 +2119,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Dimensional Modeling, Dimension Tables, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5cdfdff452dafc</t>
+          <t>https://www.indeed.com/viewjob?jk=2830c33b549b2199</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Software Engineer - Java Full Stack &amp; AI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Shift4</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Center Valley, PA, USA USA</t>
+          <t>O'Fallon, MO, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,34 +2154,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Kafka, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41844b46aff0cb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=7e59f1d190af6811</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java Full Stack &amp; AI</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>HARVEST GROUP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, USA USA</t>
+          <t>Cincinnati, OH, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, ELT, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,24 +2199,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e59f1d190af6811</t>
+          <t>https://www.indeed.com/viewjob?jk=072ead67167c5fa8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Applications Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HARVEST GROUP</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2224,34 +2224,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072ead67167c5fa8</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2b4867303bf280</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Applications Engineer</t>
+          <t>Security Engineer (Application Security)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Blue Cross Blue Shield</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2269,42 +2269,42 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2b4867303bf280</t>
+          <t>https://www.indeed.com/viewjob?jk=c00d7a111fdf4824</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Security Engineer (Application Security)</t>
+          <t>Data Engineer I - Data Platform</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00d7a111fdf4824</t>
+          <t>https://www.indeed.com/viewjob?jk=cedacf7246745512</t>
         </is>
       </c>
     </row>
@@ -2416,17 +2416,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Platform</t>
+          <t>Senior Software Engineer - DevOps (Plex)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Mayfield Heights, OH, USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Kafka, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2444,24 +2444,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9968e46f0d946d92</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8cadc6544ff917</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - DevOps (Plex)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mayfield Heights, OH, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2479,24 +2479,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad8cadc6544ff917</t>
+          <t>https://www.indeed.com/viewjob?jk=e4483784feda6d19</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Friant &amp; Associates</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>San Leandro, CA, USA USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2504,69 +2504,69 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4483784feda6d19</t>
+          <t>https://www.indeed.com/viewjob?jk=d4182938ad6c7715</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Friant &amp; Associates</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Leandro, CA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4182938ad6c7715</t>
+          <t>https://www.indeed.com/viewjob?jk=a034f20a9a1e8675</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OptionMetrics</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2574,34 +2574,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d92cc7208b2a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=78a08ffb456de840</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Cloud Infrastructure &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Storm3</t>
+          <t>OptionMetrics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,24 +2619,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06e499ccf997308</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d92cc7208b2a4a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Development Systems Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Storm3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2644,34 +2644,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671aed3088e72832</t>
+          <t>https://www.indeed.com/viewjob?jk=f06e499ccf997308</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Development Systems Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2689,24 +2689,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a034f20a9a1e8675</t>
+          <t>https://www.indeed.com/viewjob?jk=671aed3088e72832</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Service Delivery Center, Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Raleigh, NC, USA USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2724,24 +2724,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a08ffb456de840</t>
+          <t>https://www.indeed.com/viewjob?jk=b8889c03578c4693</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Senior DevOps Engineer</t>
+          <t>Software Development Engineer III - Java Stack</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2759,24 +2759,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8889c03578c4693</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a67dcea3b9163a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Development Engineer III - Java Stack</t>
+          <t>Engineer, Customer Support and Analytics</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Warren, MI, USA USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,34 +2784,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a67dcea3b9163a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c2a4c12238268f0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineer, Customer Support and Analytics</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Warren, MI, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,34 +2819,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, ETL, Power BI, Tableau, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c2a4c12238268f0</t>
+          <t>https://www.indeed.com/viewjob?jk=957d4afb6a9b1121</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Software Engineer</t>
+          <t>Sr. Infrastructure Solutions Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Raleigh, NC, USA USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2854,34 +2854,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324384e3bfc85ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=d224d690c8e329fc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Infrastructure Solutions Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Raleigh, NC, USA USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2899,32 +2899,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=957d4afb6a9b1121</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7f4e300e647e15</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure Solutions Engineer</t>
+          <t>Senior Data Engineer IS - Remote</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Plainview, TX, USA USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, NoSQL, DataOps, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2934,32 +2934,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d224d690c8e329fc</t>
+          <t>https://www.indeed.com/viewjob?jk=0361db4f39d8edb9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Engineer</t>
+          <t>Senior Data Engineer - Vehicle Quality Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Warren, MI, USA USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7f4e300e647e15</t>
+          <t>https://www.indeed.com/viewjob?jk=744a3cb2d6fb585e</t>
         </is>
       </c>
     </row>
@@ -2981,12 +2981,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OneKey MLS</t>
+          <t>AnewHealth</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Farmingdale, NY, USA USA</t>
+          <t>Cleveland, OH, USA USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3004,24 +3004,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75651bec84129cee</t>
+          <t>https://www.indeed.com/viewjob?jk=9b077b090cd4d1ef</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III, Data Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AnewHealth</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cleveland, OH, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3039,24 +3039,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b077b090cd4d1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=dbdb7a9bff45af0a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Platform Operations - Remote</t>
+          <t>Databricks Platform Engineer / AI-MLOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>EAPPS TECH LLC dba Magicforce</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, DynamoDB, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3074,24 +3074,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbdb7a9bff45af0a</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf9bfd089ca9e4c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer / AI-MLOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EAPPS TECH LLC dba Magicforce</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3109,24 +3109,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf9bfd089ca9e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ba22ee549c1229</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer 2 – Java, Generative AI, RAG &amp; Cloud Engineering</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Hopkins, MN, USA USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3144,24 +3144,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ba22ee549c1229</t>
+          <t>https://www.indeed.com/viewjob?jk=fdfcf5a045e444da</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer IS - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Plainview, TX, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3169,34 +3169,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, NoSQL, DataOps, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0361db4f39d8edb9</t>
+          <t>https://www.indeed.com/viewjob?jk=02e9aac59a0c85c9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Vehicle Quality Engineering</t>
+          <t>I&amp;T Data Services Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>City of Charlotte, NC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Warren, MI, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744a3cb2d6fb585e</t>
+          <t>https://www.indeed.com/viewjob?jk=db0e9d7d87a6771b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Java, Generative AI, RAG &amp; Cloud Engineering</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Strategic Operational Solutions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hopkins, MN, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3249,24 +3249,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdfcf5a045e444da</t>
+          <t>https://www.indeed.com/viewjob?jk=1293dae16bacfe7e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>I&amp;T Data Services Analyst</t>
+          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>City of Charlotte, NC</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Malvern, PA, USA USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3284,24 +3284,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0e9d7d87a6771b</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef875202e4d9683</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Senior Web Site Developer Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Strategic Operational Solutions</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Tempe, AZ, USA USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, CI/CD, AKS, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3319,24 +3319,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1293dae16bacfe7e</t>
+          <t>https://www.indeed.com/viewjob?jk=86b7bf97bf3d08af</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Site Reliability Engineer SRE - Internationalisation</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>FUKU</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, MySQL, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3354,24 +3354,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e9aac59a0c85c9</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4d0d149bc3cb1a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
+          <t>Sr Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Equiniti</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Malvern, PA, USA USA</t>
+          <t>Woburn, MA, USA USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3389,42 +3389,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef875202e4d9683</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer SRE - Internationalisation</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>FUKU</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, MySQL, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4d0d149bc3cb1a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4b84101d3572ca</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-14.xlsx
+++ b/results/job_matches_2026-10-14.xlsx
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IT Consultant - Cloud Specialist L2</t>
+          <t>Full Stack Developer - Node/ React/ AWS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -536,77 +536,77 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hanover, NJ, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, IAM</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c5b1d05ad98c56</t>
+          <t>https://www.indeed.com/viewjob?jk=9f52c644d636f81c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Node/ React/ AWS</t>
+          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f52c644d636f81c</t>
+          <t>https://www.indeed.com/viewjob?jk=8800b92970b28dfb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
+          <t>Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Sunrise, FL, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,59 +624,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8800b92970b28dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=f41e5aaffae63b67</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise Architecture</t>
+          <t>Store AI Agent - Onshore Data Engineer (Python, Pytorch, NodeJS)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sunrise, FL, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41e5aaffae63b67</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d863cb3c38f06b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Store AI Agent - Onshore Data Engineer (Python, Pytorch, NodeJS)</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d863cb3c38f06b</t>
+          <t>https://www.indeed.com/viewjob?jk=ebad3ecf670772f2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SS - Onshore Data Engineer (Python, Pytorch)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,67 +729,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1804ca13c879a613</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9a8b94e97af78b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT DevOps Engineer (Bilingual Chinese and English)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>SpeedX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, USA USA</t>
+          <t>Montebello, CA, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a90d59b7cf9d6b41</t>
+          <t>https://www.indeed.com/viewjob?jk=91d923f0e84b3c2c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Specialist, Yield Management - GTM Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Foundation Software, Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Strongsville, OH, USA USA</t>
+          <t>Dearborn, MI, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e8721900a835a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0f50e110d31ed36a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, Data Management - East</t>
+          <t>Full-Stack Senior Developers</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Natoli Engineering</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NJ, USA USA</t>
+          <t>Saint Charles, MO, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,67 +834,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31d93ef09b2d5ada</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e928d074bdf699</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IT DevOps Engineer (Bilingual Chinese and English)</t>
+          <t>Senior IT Programmer Analyst - Cloud DevOps</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SpeedX</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montebello, CA, USA USA</t>
+          <t>Juno Beach, FL, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Glue, EMR, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d923f0e84b3c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd9a034fcfe0278</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Specialist, Yield Management - GTM Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dearborn, MI, USA USA</t>
+          <t>Adelphi, MD, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f50e110d31ed36a</t>
+          <t>https://www.indeed.com/viewjob?jk=705ae459e19365e9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Developers</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Natoli Engineering</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saint Charles, MO, USA USA</t>
+          <t>Eden Prairie, MN, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e928d074bdf699</t>
+          <t>https://www.indeed.com/viewjob?jk=1bb043241f1ba4c6</t>
         </is>
       </c>
     </row>
@@ -981,17 +981,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer Senior Consultant I</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,24 +1009,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bb043241f1ba4c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e045cc6a43c6b4be</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer - Senior Associate</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,34 +1034,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e213d5c6c5856442</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1d2c2073e68479</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Adelphi, MD, USA USA</t>
+          <t>Bloomfield, CT, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,42 +1069,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Databricks, Hive, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705ae459e19365e9</t>
+          <t>https://www.indeed.com/viewjob?jk=845abd06a31c4d9f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer Senior Consultant I</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,24 +1114,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e045cc6a43c6b4be</t>
+          <t>https://www.indeed.com/viewjob?jk=d106c1338953198c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>DevOps / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>Alchemy Cloud</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, GCP, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d106c1338953198c</t>
+          <t>https://www.indeed.com/viewjob?jk=5fb1e7413def7791</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps / Infrastructure Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alchemy Cloud</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Adelphi, MD, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, GCP, MySQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb1e7413def7791</t>
+          <t>https://www.indeed.com/viewjob?jk=c1eb27537b9273b0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Health Data Modeler</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Adelphi, MD, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,19 +1219,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1eb27537b9273b0</t>
+          <t>https://www.indeed.com/viewjob?jk=339b2689dab59d45</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Health Data Modeler</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,77 +1254,77 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=339b2689dab59d45</t>
+          <t>https://www.indeed.com/viewjob?jk=faf7d5b09dec217c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Mutual of Omaha Mortgage</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Snowflake, SQL Server, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf7d5b09dec217c</t>
+          <t>https://www.indeed.com/viewjob?jk=d76024005e194d69</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Engineer II</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, USA USA</t>
+          <t>Woodbury, MN, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c476b35c41be97e</t>
+          <t>https://www.indeed.com/viewjob?jk=d3fed584e13523eb</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Somerville, MA, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,34 +1349,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=954d7871d42f0836</t>
+          <t>https://www.indeed.com/viewjob?jk=bcde93afa2a0a867</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mutual of Omaha Mortgage</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,17 +1384,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Snowflake, SQL Server, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d76024005e194d69</t>
+          <t>https://www.indeed.com/viewjob?jk=954d7871d42f0836</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UKG Integration Developer</t>
+          <t>Salesforce Developer. Jr./Mid/Sr. - U.S Citizen &amp; DOD clearance</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vnsure Business Solution</t>
+          <t>Vissat Solutions, Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd00894ae3ccf24</t>
+          <t>https://www.indeed.com/viewjob?jk=517d7c52f9207896</t>
         </is>
       </c>
     </row>
@@ -1506,25 +1506,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Engineer Data II</t>
+          <t>Sr. Support &amp; Post-Release Quality Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IGT</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, USA USA</t>
+          <t>Berkeley Heights, NJ, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,24 +1534,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da8f75cf9c2b540</t>
+          <t>https://www.indeed.com/viewjob?jk=5898f422bfe5208e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer - Materials Discovery Research Institute</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UL Research Institutes</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Skokie, IL, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,24 +1569,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01d33f572b2baf0</t>
+          <t>https://www.indeed.com/viewjob?jk=cfda204c96b0612c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Engineer Data II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>IGT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Las Vegas, NV, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,24 +1604,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d247a00ef97cfce</t>
+          <t>https://www.indeed.com/viewjob?jk=0da8f75cf9c2b540</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack &amp; AI</t>
+          <t>Data Engineer - Materials Discovery Research Institute</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>UL Research Institutes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, USA USA</t>
+          <t>Skokie, IL, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,24 +1639,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadfe87c770bfddc</t>
+          <t>https://www.indeed.com/viewjob?jk=f01d33f572b2baf0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Louisville, KY, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,34 +1664,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6352c20c3850230b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d247a00ef97cfce</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II - Full Stack &amp; AI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>O'Fallon, MO, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,34 +1699,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2de87a09b47cb83</t>
+          <t>https://www.indeed.com/viewjob?jk=eadfe87c770bfddc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IT Analyst III - Database Administrator</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>State of Utah</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Taylorsville, UT, USA USA</t>
+          <t>Louisville, KY, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,42 +1734,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0318ab669e83c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=6352c20c3850230b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>IT Analyst III - Database Administrator</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>State of Utah</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, USA USA</t>
+          <t>Taylorsville, UT, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,24 +1779,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=f0318ab669e83c7d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jr. Cloud Automation Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Sunnyvale, CA, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,34 +1804,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, DataOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c700c5ee304c350</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d31bded3f1a6c4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>.Net Engineer</t>
+          <t>Jr. Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tampa, FL, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,24 +1849,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dded0af6d2070543</t>
+          <t>https://www.indeed.com/viewjob?jk=5c700c5ee304c350</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Platform Administrator</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AllianceBernstein</t>
+          <t>AutoNation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, USA USA</t>
+          <t>Fort Lauderdale, FL, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,17 +1874,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Vertex AI, Scala, Snowflake, Data Modeling, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, PostgreSQL, MySQL, DynamoDB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae65d4effd1829d</t>
+          <t>https://www.indeed.com/viewjob?jk=069ede0c0f4092ec</t>
         </is>
       </c>
     </row>
@@ -1926,17 +1926,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>SJSU Research Foundation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>San Jose, CA, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Dimensional Modeling, Dimension Tables, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, Scala, Snowflake, Oracle, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,24 +1954,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5cdfdff452dafc</t>
+          <t>https://www.indeed.com/viewjob?jk=e1de3366eafd1cc6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SJSU Research Foundation</t>
+          <t>Naviga Publishing Solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Jose, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, Scala, Snowflake, Oracle, ETL, ELT, Tableau</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,24 +1989,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1de3366eafd1cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=d2e6c94bac794111</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Marketing Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Shift4</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Center Valley, PA, USA USA</t>
+          <t>La Mirada, CA, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Kafka, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,24 +2024,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41844b46aff0cb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=91f01e86c7eb2733</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Marketing Data Engineer</t>
+          <t>Senior Databrick Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>SDG Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>La Mirada, CA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f01e86c7eb2733</t>
+          <t>https://www.indeed.com/viewjob?jk=3e85cb5ceb58b2cf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Databrick Data Engineering Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SDG Group</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,34 +2084,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Dimensional Modeling, Dimension Tables, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e85cb5ceb58b2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5cdfdff452dafc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Software Engineer - Java Full Stack &amp; AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Solero Workforce Solutions</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FL, USA USA</t>
+          <t>O'Fallon, MO, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,34 +2119,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2830c33b549b2199</t>
+          <t>https://www.indeed.com/viewjob?jk=dbc5b57747195bb1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java Full Stack &amp; AI</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>HARVEST GROUP</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, USA USA</t>
+          <t>Cincinnati, OH, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, ELT, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,24 +2164,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e59f1d190af6811</t>
+          <t>https://www.indeed.com/viewjob?jk=072ead67167c5fa8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HARVEST GROUP</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, USA USA</t>
+          <t>Columbus, OH, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072ead67167c5fa8</t>
+          <t>https://www.indeed.com/viewjob?jk=d315872cc7738b0e</t>
         </is>
       </c>
     </row>
@@ -2241,52 +2241,52 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Security Engineer (Application Security)</t>
+          <t>Data Engineer I - Data Platform</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00d7a111fdf4824</t>
+          <t>https://www.indeed.com/viewjob?jk=cedacf7246745512</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer I - Data Platform</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>AltorOne Technologies</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, USA USA</t>
+          <t>Fayetteville, NC, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Cloud Storage, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cedacf7246745512</t>
+          <t>https://www.indeed.com/viewjob?jk=887e0b7374cefb19</t>
         </is>
       </c>
     </row>
@@ -2346,17 +2346,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mountain View, CA, USA USA</t>
+          <t>Munster, IN, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Databricks, GCP, Spark, Kafka, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,24 +2374,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc0f0441157327ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c8f37e817406df46</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Mountain View, CA, USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,34 +2399,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Terraform</t>
+          <t>AWS, EMR, S3, RDS, Azure, Databricks, GCP, Spark, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb2022242ed43e7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc0f0441157327ec</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - DevOps (Plex)</t>
+          <t>AI Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mayfield Heights, OH, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,34 +2434,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ELT, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad8cadc6544ff917</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7efb07423344e6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AWS Connect Engineer with Genesys</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Plano, TX, USA USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,34 +2469,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4483784feda6d19</t>
+          <t>https://www.indeed.com/viewjob?jk=6294736244722aeb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer - DevOps (Plex)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Friant &amp; Associates</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Leandro, CA, USA USA</t>
+          <t>Mayfield Heights, OH, USA USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2504,42 +2504,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Kafka, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4182938ad6c7715</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8cadc6544ff917</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,42 +2549,42 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a034f20a9a1e8675</t>
+          <t>https://www.indeed.com/viewjob?jk=e4483784feda6d19</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Friant &amp; Associates</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>San Leandro, CA, USA USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a08ffb456de840</t>
+          <t>https://www.indeed.com/viewjob?jk=d4182938ad6c7715</t>
         </is>
       </c>
     </row>
@@ -2696,17 +2696,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Senior DevOps Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8889c03578c4693</t>
+          <t>https://www.indeed.com/viewjob?jk=a034f20a9a1e8675</t>
         </is>
       </c>
     </row>
@@ -2801,17 +2801,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Infrastructure Solutions Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Raleigh, NC, USA USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=957d4afb6a9b1121</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7f4e300e647e15</t>
         </is>
       </c>
     </row>
@@ -2871,52 +2871,52 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Engineer</t>
+          <t>Data Engineer - Mid-Level</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>Rockville, MD, USA USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7f4e300e647e15</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ccf3f575e5d36b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer IS - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>AnewHealth</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Plainview, TX, USA USA</t>
+          <t>Cleveland, OH, USA USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, NoSQL, DataOps, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2934,24 +2934,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0361db4f39d8edb9</t>
+          <t>https://www.indeed.com/viewjob?jk=9b077b090cd4d1ef</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Vehicle Quality Engineering</t>
+          <t>Software Engineer III, Data Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Warren, MI, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, CI/CD, Git, Python</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2969,24 +2969,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744a3cb2d6fb585e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbdb7a9bff45af0a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Platform Engineer / AI-MLOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AnewHealth</t>
+          <t>EAPPS TECH LLC dba Magicforce</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cleveland, OH, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3004,24 +3004,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b077b090cd4d1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf9bfd089ca9e4c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Platform Operations - Remote</t>
+          <t>Senior Data Engineer IS - Remote</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, USA USA</t>
+          <t>Plainview, TX, USA USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, DynamoDB, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, NoSQL, DataOps, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3039,24 +3039,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbdb7a9bff45af0a</t>
+          <t>https://www.indeed.com/viewjob?jk=0361db4f39d8edb9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer / AI-MLOps Engineer</t>
+          <t>Senior Data Engineer - Vehicle Quality Engineering</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EAPPS TECH LLC dba Magicforce</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Warren, MI, USA USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3074,24 +3074,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf9bfd089ca9e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=744a3cb2d6fb585e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, ELT, CI/CD</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ba22ee549c1229</t>
+          <t>https://www.indeed.com/viewjob?jk=60fb6c37a0a7b7f8</t>
         </is>
       </c>
     </row>
@@ -3186,17 +3186,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>I&amp;T Data Services Analyst</t>
+          <t>BI Specialist II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>City of Charlotte, NC</t>
+          <t>ScanSource</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Greenville, SC, USA USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3204,34 +3204,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0e9d7d87a6771b</t>
+          <t>https://www.indeed.com/viewjob?jk=654d639496cd0389</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>I&amp;T Data Services Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Strategic Operational Solutions</t>
+          <t>City of Charlotte, NC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3249,24 +3249,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1293dae16bacfe7e</t>
+          <t>https://www.indeed.com/viewjob?jk=db0e9d7d87a6771b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Malvern, PA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3274,34 +3274,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef875202e4d9683</t>
+          <t>https://www.indeed.com/viewjob?jk=2afaeff725cfa829</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Web Site Developer Engineer</t>
+          <t>Java Developer with React</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tempe, AZ, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3309,34 +3309,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, CI/CD, AKS, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86b7bf97bf3d08af</t>
+          <t>https://www.indeed.com/viewjob?jk=e1346e9fc73ad3d4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer SRE - Internationalisation</t>
+          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FUKU</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Malvern, PA, USA USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3344,34 +3344,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, MySQL, Kubernetes, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4d0d149bc3cb1a</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef875202e4d9683</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer</t>
+          <t>Site Reliability Engineer SRE - Internationalisation</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Equiniti</t>
+          <t>FUKU</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Woburn, MA, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, MySQL, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4b84101d3572ca</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4d0d149bc3cb1a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-14.xlsx
+++ b/results/job_matches_2026-10-14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,60 +491,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Systems Architect - TS/SCI w/ Poly required</t>
+          <t>Full Stack Developer - Node/ React/ AWS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Warrenton, VA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.6</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b2560066a45e46</t>
+          <t>https://www.indeed.com/viewjob?jk=9f52c644d636f81c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Node/ React/ AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Anvi Corp Usa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Plano, TX, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Lambda, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,24 +554,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f52c644d636f81c</t>
+          <t>https://www.indeed.com/viewjob?jk=b908b59309fff889</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
+          <t>Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Sunrise, FL, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,7 +579,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,59 +589,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8800b92970b28dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=f41e5aaffae63b67</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise Architecture</t>
+          <t>Store AI Agent - Onshore Data Engineer (Python, Pytorch, NodeJS)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunrise, FL, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41e5aaffae63b67</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d863cb3c38f06b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Store AI Agent - Onshore Data Engineer (Python, Pytorch, NodeJS)</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,42 +659,42 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d863cb3c38f06b</t>
+          <t>https://www.indeed.com/viewjob?jk=ebad3ecf670772f2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>IT DevOps Engineer (Bilingual Chinese and English)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>SpeedX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Montebello, CA, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebad3ecf670772f2</t>
+          <t>https://www.indeed.com/viewjob?jk=91d923f0e84b3c2c</t>
         </is>
       </c>
     </row>
@@ -706,20 +706,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Trisura</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, USA USA</t>
+          <t>Oklahoma City, OK, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,129 +729,129 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9a8b94e97af78b</t>
+          <t>https://www.indeed.com/viewjob?jk=b51afc5191d0fbc5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT DevOps Engineer (Bilingual Chinese and English)</t>
+          <t>Senior IT Programmer Analyst - Cloud DevOps</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SpeedX</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Montebello, CA, USA USA</t>
+          <t>Juno Beach, FL, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL, Splunk</t>
+          <t>AWS, Glue, EMR, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d923f0e84b3c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd9a034fcfe0278</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Specialist, Yield Management - GTM Data Engineer</t>
+          <t>Business Intelligence Data Modeler Engineer Senior I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dearborn, MI, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f50e110d31ed36a</t>
+          <t>https://www.indeed.com/viewjob?jk=3a79945a69d44134</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Developers</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Natoli Engineering</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saint Charles, MO, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e928d074bdf699</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1d2c2073e68479</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior IT Programmer Analyst - Cloud DevOps</t>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Juno Beach, FL, USA USA</t>
+          <t>Bloomfield, CT, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Databricks, Hive, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,102 +869,102 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd9a034fcfe0278</t>
+          <t>https://www.indeed.com/viewjob?jk=845abd06a31c4d9f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Adelphi, MD, USA USA</t>
+          <t>Somerville, MA, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705ae459e19365e9</t>
+          <t>https://www.indeed.com/viewjob?jk=bcde93afa2a0a867</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mutual of Omaha Mortgage</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Snowflake, SQL Server, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bb043241f1ba4c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d76024005e194d69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Modeler Engineer Senior I</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Woodbury, MN, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,102 +974,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a79945a69d44134</t>
+          <t>https://www.indeed.com/viewjob?jk=d3fed584e13523eb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer Senior Consultant I</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Pennant Solutions Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Richmond, VA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e045cc6a43c6b4be</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c84e90f22435c1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Operations Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>IHG Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, Data Modeling, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1d2c2073e68479</t>
+          <t>https://www.indeed.com/viewjob?jk=a595a72e3d3f9968</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor- Hybrid</t>
+          <t>Salesforce Developer. Jr./Mid/Sr. - U.S Citizen &amp; DOD clearance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Vissat Solutions, Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Databricks, Hive, Spark, Scala, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,102 +1079,102 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845abd06a31c4d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=517d7c52f9207896</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Wilmington, DE, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d106c1338953198c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7261f813c68e65e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps / Infrastructure Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alchemy Cloud</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, GCP, MySQL, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb1e7413def7791</t>
+          <t>https://www.indeed.com/viewjob?jk=cfda204c96b0612c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Engineer Data II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>IGT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Adelphi, MD, USA USA</t>
+          <t>Las Vegas, NV, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,102 +1184,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1eb27537b9273b0</t>
+          <t>https://www.indeed.com/viewjob?jk=0da8f75cf9c2b540</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Health Data Modeler</t>
+          <t>Data Engineer - Materials Discovery Research Institute</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>UL Research Institutes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Skokie, IL, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=339b2689dab59d45</t>
+          <t>https://www.indeed.com/viewjob?jk=f01d33f572b2baf0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Louisville, KY, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, ELT</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf7d5b09dec217c</t>
+          <t>https://www.indeed.com/viewjob?jk=6352c20c3850230b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mutual of Omaha Mortgage</t>
+          <t>Tomorrow.io</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>Golden, CO, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Snowflake, SQL Server, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, Lambda, S3, SQS, Azure, GCP, MongoDB, NoSQL, Data Modeling, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,67 +1289,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d76024005e194d69</t>
+          <t>https://www.indeed.com/viewjob?jk=79c299784b27caa7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>IT Analyst III - Database Administrator</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>State of Utah</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Woodbury, MN, USA USA</t>
+          <t>Taylorsville, UT, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3fed584e13523eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f0318ab669e83c7d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Somerville, MA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,19 +1359,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcde93afa2a0a867</t>
+          <t>https://www.indeed.com/viewjob?jk=fc746cb98ddc1200</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – Microsoft Fabric &amp; Healthcare Integrations</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Quantum Pain &amp; Sports Medicine</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1380,46 +1380,46 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>EMR, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=954d7871d42f0836</t>
+          <t>https://www.indeed.com/viewjob?jk=23426a1bd3bfe56b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pennant Solutions Group</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, USA USA</t>
+          <t>Sunnyvale, CA, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, DataOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,32 +1429,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c84e90f22435c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d31bded3f1a6c4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Salesforce Developer. Jr./Mid/Sr. - U.S Citizen &amp; DOD clearance</t>
+          <t>Senior Data Platform Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vissat Solutions, Inc</t>
+          <t>AutoNation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Fort Lauderdale, FL, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, PostgreSQL, MySQL, DynamoDB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,172 +1464,172 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=517d7c52f9207896</t>
+          <t>https://www.indeed.com/viewjob?jk=069ede0c0f4092ec</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IHG Hotels &amp; Resorts</t>
+          <t>SJSU Research Foundation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>San Jose, CA, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, Data Modeling, Jenkins</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, Scala, Snowflake, Oracle, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a595a72e3d3f9968</t>
+          <t>https://www.indeed.com/viewjob?jk=e1de3366eafd1cc6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Support &amp; Post-Release Quality Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Naviga Publishing Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5898f422bfe5208e</t>
+          <t>https://www.indeed.com/viewjob?jk=d2e6c94bac794111</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Databrick Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>SDG Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfda204c96b0612c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e85cb5ceb58b2cf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer Data II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IGT</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Dimensional Modeling, Dimension Tables, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da8f75cf9c2b540</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5cdfdff452dafc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - Materials Discovery Research Institute</t>
+          <t>Senior Software Engineer - Java Full Stack &amp; AI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UL Research Institutes</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Skokie, IL, USA USA</t>
+          <t>O'Fallon, MO, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,67 +1639,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01d33f572b2baf0</t>
+          <t>https://www.indeed.com/viewjob?jk=dbc5b57747195bb1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>DevSecOps Engineer (Part-Time)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Techsur Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d247a00ef97cfce</t>
+          <t>https://www.indeed.com/viewjob?jk=31d8c0af8aa1050b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack &amp; AI</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>HARVEST GROUP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, USA USA</t>
+          <t>Cincinnati, OH, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,32 +1709,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadfe87c770bfddc</t>
+          <t>https://www.indeed.com/viewjob?jk=072ead67167c5fa8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Louisville, KY, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, RDS, Snowflake, Tableau, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,32 +1744,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6352c20c3850230b</t>
+          <t>https://www.indeed.com/viewjob?jk=59537b765c557b2d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IT Analyst III - Database Administrator</t>
+          <t>Senior Software Applications Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>State of Utah</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Taylorsville, UT, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,32 +1779,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0318ab669e83c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2b4867303bf280</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer I - Data Platform</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Intuitive (Intuitive Surgical)</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, DataOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,67 +1814,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d31bded3f1a6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=cedacf7246745512</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jr. Cloud Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c700c5ee304c350</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4aaf4d33a99fad</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Platform Administrator</t>
+          <t>Cloud Data Engineer - AI Platform</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AutoNation</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, PostgreSQL, MySQL, DynamoDB, Data Modeling, ELT</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,67 +1884,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069ede0c0f4092ec</t>
+          <t>https://www.indeed.com/viewjob?jk=6af71823f4081c08</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>o3 Solutions</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Lebanon, NJ, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea8f0126c1468fe</t>
+          <t>https://www.indeed.com/viewjob?jk=d3f6955e62075655</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SJSU Research Foundation</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Jose, CA, USA USA</t>
+          <t>Munster, IN, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, Scala, Snowflake, Oracle, ETL, ELT, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,19 +1954,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1de3366eafd1cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=c8f37e817406df46</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>AI Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Naviga Publishing Solutions</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1975,11 +1975,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ELT, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,102 +1989,102 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2e6c94bac794111</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7efb07423344e6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marketing Data Engineer</t>
+          <t>Senior Data &amp; Software Engineer (Java / GCP) (contract)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>La Mirada, CA, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, dbt, Power BI</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f01e86c7eb2733</t>
+          <t>https://www.indeed.com/viewjob?jk=37e78a01bc07e041</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Databrick Data Engineering Consultant</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SDG Group</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Mountain View, CA, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, S3, RDS, Azure, Databricks, GCP, Spark, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e85cb5ceb58b2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=fc0f0441157327ec</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Connect Engineer with Genesys</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Plano, TX, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Dimensional Modeling, Dimension Tables, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,32 +2094,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5cdfdff452dafc</t>
+          <t>https://www.indeed.com/viewjob?jk=6294736244722aeb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java Full Stack &amp; AI</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Friant &amp; Associates</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, USA USA</t>
+          <t>San Leandro, CA, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, ELT, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,32 +2129,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbc5b57747195bb1</t>
+          <t>https://www.indeed.com/viewjob?jk=d4182938ad6c7715</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HARVEST GROUP</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, USA USA</t>
+          <t>Brooklyn Park, MN, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,32 +2164,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072ead67167c5fa8</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef2140069fbbe73</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Scientific Applications Software Engineering I</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>NASA Jet Propulsion Laboratory</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, USA USA</t>
+          <t>Pasadena, CA, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,67 +2199,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d315872cc7738b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=14c9b41460681a7a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Applications Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>ALTANA AG</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, PySpark, ELT, MLflow, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2b4867303bf280</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3f63c42f2039db</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer I - Data Platform</t>
+          <t>Cloud Infrastructure &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>OptionMetrics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2269,32 +2269,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cedacf7246745512</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d92cc7208b2a4a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer (w/ Oracle &amp; OLTP)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AltorOne Technologies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fayetteville, NC, USA USA</t>
+          <t>Nashville, TN, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Cloud Storage, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,32 +2304,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887e0b7374cefb19</t>
+          <t>https://www.indeed.com/viewjob?jk=82a5c0ffe75e0df7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Atlas Air, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, USA USA</t>
+          <t>Fort Lauderdale, FL, USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,32 +2339,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3f6955e62075655</t>
+          <t>https://www.indeed.com/viewjob?jk=c0292ff70f1110f6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Storm3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Munster, IN, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,32 +2374,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8f37e817406df46</t>
+          <t>https://www.indeed.com/viewjob?jk=f06e499ccf997308</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>UrbanVest Technologies</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mountain View, CA, USA USA</t>
+          <t>Milwaukee, WI, USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Databricks, GCP, Spark, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,67 +2409,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc0f0441157327ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a0085b8c8e54f8d4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Cloud Platform Engineer</t>
+          <t>Software Development Engineer III - Java Stack</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ELT, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7efb07423344e6</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a67dcea3b9163a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Connect Engineer with Genesys</t>
+          <t>Engineer, Customer Support and Analytics</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, USA USA</t>
+          <t>Warren, MI, USA USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2479,102 +2479,102 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6294736244722aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=4c2a4c12238268f0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - DevOps (Plex)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mayfield Heights, OH, USA USA</t>
+          <t>Bethesda, MD, USA USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, MLOps, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad8cadc6544ff917</t>
+          <t>https://www.indeed.com/viewjob?jk=2a322578c891277c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack .NET Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>RDS, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4483784feda6d19</t>
+          <t>https://www.indeed.com/viewjob?jk=324384e3bfc85ae8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer - Mid-Level</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Friant &amp; Associates</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Leandro, CA, USA USA</t>
+          <t>Rockville, MD, USA USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4182938ad6c7715</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ccf3f575e5d36b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; DevOps Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OptionMetrics</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Bethesda, MD, USA USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Cassandra, NoSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d92cc7208b2a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=c933d7fccfe836ff</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Storm3</t>
+          <t>Waste Connections</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>The Woodlands, TX, USA USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,67 +2654,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06e499ccf997308</t>
+          <t>https://www.indeed.com/viewjob?jk=5e29cc918dda3a0b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Development Systems Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Wake Forest University</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Winston-Salem, NC, USA USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, GCP, Snowflake, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671aed3088e72832</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e176375898329e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2724,164 +2724,164 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a034f20a9a1e8675</t>
+          <t>https://www.indeed.com/viewjob?jk=60fb6c37a0a7b7f8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Development Engineer III - Java Stack</t>
+          <t>BI Specialist II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>ScanSource</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Greenville, SC, USA USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a67dcea3b9163a</t>
+          <t>https://www.indeed.com/viewjob?jk=654d639496cd0389</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer, Customer Support and Analytics</t>
+          <t>I&amp;T Data Services Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>City of Charlotte, NC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Warren, MI, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, ETL, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c2a4c12238268f0</t>
+          <t>https://www.indeed.com/viewjob?jk=db0e9d7d87a6771b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Engineer</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7f4e300e647e15</t>
+          <t>https://www.indeed.com/viewjob?jk=2afaeff725cfa829</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure Solutions Engineer</t>
+          <t>Java Developer with React</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d224d690c8e329fc</t>
+          <t>https://www.indeed.com/viewjob?jk=e1346e9fc73ad3d4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid-Level</t>
+          <t>Site Reliability Engineer SRE - Internationalisation</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>FUKU</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rockville, MD, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, MySQL, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2898,496 +2898,6 @@
         </is>
       </c>
       <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ccf3f575e5d36b</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>AnewHealth</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, USA USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b077b090cd4d1ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Software Engineer III, Data Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, USA USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, DynamoDB, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dbdb7a9bff45af0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Databricks Platform Engineer / AI-MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>EAPPS TECH LLC dba Magicforce</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Chicago, IL, USA USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf9bfd089ca9e4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer IS - Remote</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Providence</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Plainview, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, NoSQL, DataOps, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0361db4f39d8edb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Vehicle Quality Engineering</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Warren, MI, USA USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=744a3cb2d6fb585e</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Curana Health</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60fb6c37a0a7b7f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Software Engineer 2 – Java, Generative AI, RAG &amp; Cloud Engineering</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Hopkins, MN, USA USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdfcf5a045e444da</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Dallas, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02e9aac59a0c85c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>BI Specialist II</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>ScanSource</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Greenville, SC, USA USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, Data Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=654d639496cd0389</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>I&amp;T Data Services Analyst</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>City of Charlotte, NC</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, USA USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db0e9d7d87a6771b</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Data Infrastructure Architect</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2afaeff725cfa829</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Java Developer with React</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Chicago, IL, USA USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1346e9fc73ad3d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Siemens Healthineers</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Malvern, PA, USA USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef875202e4d9683</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer SRE - Internationalisation</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>FUKU</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, MySQL, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fc4d0d149bc3cb1a</t>
         </is>
